--- a/data/evolucao.xlsx
+++ b/data/evolucao.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30021"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B546B59-3CBF-471F-92FB-DA4C7FDA7F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719612BB-178F-4CFB-8F3A-70A1B6355A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7EB965E4-CD38-43F5-AB1D-C85E27C9787B}"/>
   </bookViews>
@@ -580,7 +580,12 @@
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
@@ -608,7 +613,12 @@
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
@@ -636,9 +646,12 @@
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="M4" s="5"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="2"/>
       <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
@@ -666,9 +679,12 @@
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="2"/>
       <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
@@ -696,9 +712,12 @@
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="M6" s="5"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="2"/>
       <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
@@ -726,9 +745,12 @@
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="M7" s="5"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="2"/>
       <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
@@ -756,9 +778,12 @@
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="M8" s="5"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="2"/>
       <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
@@ -786,9 +811,12 @@
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="M9" s="5"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="2"/>
       <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
     </row>
@@ -818,9 +846,12 @@
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="M10" s="5"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="2"/>
       <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
     </row>
@@ -850,9 +881,12 @@
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="M11" s="5"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="2"/>
       <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
     </row>
@@ -882,9 +916,12 @@
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="M12" s="5"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="2"/>
       <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
     </row>
@@ -914,9 +951,10 @@
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="5"/>
       <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
+      <c r="M13" s="2"/>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
       <c r="P13" s="5"/>
@@ -948,9 +986,10 @@
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="5"/>
       <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
+      <c r="M14" s="2"/>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
@@ -982,8 +1021,10 @@
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="M15" s="5"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="2"/>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
       <c r="P15" s="5"/>
@@ -1015,8 +1056,10 @@
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="M16" s="5"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="2"/>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
@@ -1048,9 +1091,12 @@
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="M17" s="5"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="2"/>
       <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
       <c r="P17" s="5"/>
       <c r="Q17" s="5"/>
     </row>
@@ -1080,9 +1126,12 @@
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="M18" s="5"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="2"/>
       <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
     </row>
@@ -1112,9 +1161,12 @@
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="M19" s="5"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="2"/>
       <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
       <c r="R19" s="2"/>
@@ -1173,9 +1225,12 @@
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="M20" s="5"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="2"/>
       <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
@@ -1234,9 +1289,12 @@
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="M21" s="5"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="2"/>
       <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
@@ -1295,9 +1353,12 @@
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="M22" s="5"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="2"/>
       <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
     </row>
@@ -1327,9 +1388,12 @@
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="M23" s="5"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="2"/>
       <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
     </row>
@@ -1341,7 +1405,7 @@
         <v>4.0777428669542379</v>
       </c>
       <c r="C24" s="5">
-        <f>B24+C23</f>
+        <f t="shared" ref="C24:C35" si="2">B24+C23</f>
         <v>61.88359721313001</v>
       </c>
       <c r="D24" s="5">
@@ -1359,8 +1423,10 @@
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="M24" s="5"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="2"/>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
       <c r="P24" s="5"/>
@@ -1371,11 +1437,11 @@
         <v>46142</v>
       </c>
       <c r="B25" s="5">
-        <v>3.8840481318507378</v>
+        <v>3.5014922950882301</v>
       </c>
       <c r="C25" s="5">
-        <f>B25+C24</f>
-        <v>65.76764534498075</v>
+        <f t="shared" si="2"/>
+        <v>65.385089508218243</v>
       </c>
       <c r="D25" s="5">
         <v>3.8541290585101118</v>
@@ -1392,9 +1458,11 @@
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="M25" s="5"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
       <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
     </row>
@@ -1403,11 +1471,11 @@
         <v>46173</v>
       </c>
       <c r="B26" s="5">
-        <v>4.3761330261136422</v>
+        <v>3.8531711558524697</v>
       </c>
       <c r="C26" s="5">
-        <f>B26+C25</f>
-        <v>70.143778371094385</v>
+        <f t="shared" si="2"/>
+        <v>69.238260664070708</v>
       </c>
       <c r="D26" s="5">
         <v>5.609521778535119</v>
@@ -1424,9 +1492,11 @@
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="M26" s="5"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
       <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
@@ -1464,11 +1534,11 @@
         <v>46203</v>
       </c>
       <c r="B27" s="5">
-        <v>4.7787989303792289</v>
+        <v>4.6786247600919797</v>
       </c>
       <c r="C27" s="5">
-        <f>B27+C26</f>
-        <v>74.922577301473609</v>
+        <f t="shared" si="2"/>
+        <v>73.916885424162686</v>
       </c>
       <c r="D27" s="5">
         <v>3.6604000147033013</v>
@@ -1485,9 +1555,11 @@
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="M27" s="5"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
       <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
       <c r="P27" s="5"/>
       <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
@@ -1525,11 +1597,11 @@
         <v>46234</v>
       </c>
       <c r="B28" s="5">
-        <v>7.0330138737099395</v>
+        <v>7.01</v>
       </c>
       <c r="C28" s="5">
-        <f>B28+C27</f>
-        <v>81.955591175183542</v>
+        <f t="shared" si="2"/>
+        <v>80.926885424162691</v>
       </c>
       <c r="D28" s="5">
         <v>4.7754104889294844</v>
@@ -1546,9 +1618,11 @@
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="M28" s="5"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
       <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
     </row>
@@ -1557,11 +1631,11 @@
         <v>46265</v>
       </c>
       <c r="B29" s="5">
-        <v>5.8761378340335026</v>
+        <v>6.0968221609415796</v>
       </c>
       <c r="C29" s="5">
-        <f>B29+C28</f>
-        <v>87.831729009217042</v>
+        <f t="shared" si="2"/>
+        <v>87.023707585104276</v>
       </c>
       <c r="D29" s="5">
         <v>4.6533975272671508</v>
@@ -1578,9 +1652,11 @@
       </c>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="M29" s="5"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
       <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
       <c r="P29" s="5"/>
       <c r="Q29" s="5"/>
     </row>
@@ -1589,11 +1665,11 @@
         <v>46295</v>
       </c>
       <c r="B30" s="5">
-        <v>3.5364227254632294</v>
+        <v>3.7564913195156415</v>
       </c>
       <c r="C30" s="5">
-        <f>B30+C29</f>
-        <v>91.368151734680268</v>
+        <f t="shared" si="2"/>
+        <v>90.780198904619922</v>
       </c>
       <c r="D30" s="5">
         <v>4.7101274741177823</v>
@@ -1610,9 +1686,11 @@
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="M30" s="5"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
       <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
     </row>
@@ -1621,11 +1699,11 @@
         <v>46326</v>
       </c>
       <c r="B31" s="5">
-        <v>4.0707772539267175</v>
+        <v>4.4727637918657246</v>
       </c>
       <c r="C31" s="5">
-        <f>B31+C30</f>
-        <v>95.438928988606989</v>
+        <f t="shared" si="2"/>
+        <v>95.252962696485653</v>
       </c>
       <c r="D31" s="5">
         <v>3.3851885105485091</v>
@@ -1642,9 +1720,11 @@
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="M31" s="5"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
       <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
       <c r="P31" s="5"/>
       <c r="Q31" s="5"/>
     </row>
@@ -1653,11 +1733,11 @@
         <v>46356</v>
       </c>
       <c r="B32" s="5">
-        <v>1.7542652278114175</v>
+        <v>1.8648397094426086</v>
       </c>
       <c r="C32" s="5">
-        <f>B32+C31</f>
-        <v>97.193194216418405</v>
+        <f t="shared" si="2"/>
+        <v>97.117802405928259</v>
       </c>
       <c r="D32" s="5">
         <v>1.6260930386958057</v>
@@ -1674,9 +1754,11 @@
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="M32" s="5"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
       <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
       <c r="P32" s="5"/>
       <c r="Q32" s="5"/>
     </row>
@@ -1685,11 +1767,11 @@
         <v>46387</v>
       </c>
       <c r="B33" s="5">
-        <v>1.3187128168262519</v>
+        <v>1.3731745642513373</v>
       </c>
       <c r="C33" s="5">
-        <f>B33+C32</f>
-        <v>98.511907033244654</v>
+        <f t="shared" si="2"/>
+        <v>98.490976970179602</v>
       </c>
       <c r="D33" s="5">
         <v>1.0526891974688515</v>
@@ -1706,9 +1788,11 @@
       </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="M33" s="5"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
       <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
       <c r="P33" s="5"/>
       <c r="Q33" s="5"/>
     </row>
@@ -1717,11 +1801,11 @@
         <v>46418</v>
       </c>
       <c r="B34" s="5">
-        <v>1.4452320910390646</v>
+        <v>1.1970641274525655</v>
       </c>
       <c r="C34" s="5">
-        <f>B34+C33</f>
-        <v>99.957139124283714</v>
+        <f t="shared" si="2"/>
+        <v>99.688041097632166</v>
       </c>
       <c r="D34" s="5">
         <v>1.0108646273378574</v>
@@ -1738,9 +1822,11 @@
       </c>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="M34" s="5"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
       <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
     </row>
@@ -1749,11 +1835,11 @@
         <v>46446</v>
       </c>
       <c r="B35" s="5">
-        <v>4.286087571628313E-2</v>
+        <v>0.31311062960122193</v>
       </c>
       <c r="C35" s="5">
-        <f>B35+C34</f>
-        <v>100</v>
+        <f t="shared" si="2"/>
+        <v>100.00115172723339</v>
       </c>
       <c r="D35" s="5">
         <f>100-E34</f>
@@ -1771,9 +1857,11 @@
       </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="M35" s="5"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
       <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
       <c r="P35" s="5"/>
       <c r="Q35" s="5"/>
     </row>
@@ -1786,7 +1874,7 @@
       </c>
       <c r="C36" s="5">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>100.00115172723339</v>
       </c>
       <c r="D36" s="5">
         <v>0</v>
@@ -1800,59 +1888,42 @@
       <c r="G36" s="5">
         <v>100.00000000000061</v>
       </c>
-      <c r="M36" s="5"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
       <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
       <c r="P36" s="5"/>
       <c r="Q36" s="5"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="K37" s="5"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
+      <c r="L37" s="5"/>
       <c r="P37" s="5"/>
       <c r="Q37" s="5"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
       <c r="P38" s="5"/>
       <c r="Q38" s="5"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="M39" s="5"/>
-      <c r="N39" s="5"/>
       <c r="P39" s="5"/>
       <c r="Q39" s="5"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
       <c r="P40" s="5"/>
       <c r="Q40" s="5"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E41" s="6"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
       <c r="P41" s="5"/>
       <c r="Q41" s="5"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="M42" s="5"/>
       <c r="P42" s="5"/>
       <c r="Q42" s="5"/>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="M43" s="5"/>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="M44" s="5"/>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="M45" s="5"/>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="M46" s="5"/>
     </row>
     <row r="55" spans="14:15" x14ac:dyDescent="0.3">
       <c r="N55" s="5"/>
@@ -1877,12 +1948,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2030,15 +2098,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5587604-DA3E-4313-9FC4-BBB4C884AB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E7B3CB9-FAE3-4DD3-B62A-E97648FB882B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2062,10 +2134,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E7B3CB9-FAE3-4DD3-B62A-E97648FB882B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5587604-DA3E-4313-9FC4-BBB4C884AB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/evolucao.xlsx
+++ b/data/evolucao.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30021"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719612BB-178F-4CFB-8F3A-70A1B6355A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21AB1958-153C-4430-95A2-F4FA54BA7E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7EB965E4-CD38-43F5-AB1D-C85E27C9787B}"/>
   </bookViews>
@@ -499,7 +499,7 @@
   <sheetPr>
     <outlinePr summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AT58"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
@@ -509,30 +509,12 @@
     <col min="5" max="5" width="25.109375" customWidth="1"/>
     <col min="6" max="6" width="22.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="10.88671875" customWidth="1"/>
-    <col min="13" max="13" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="10" bestFit="1" customWidth="1"/>
-    <col min="21" max="27" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="35" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="42" width="10" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="10" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="10.88671875" customWidth="1"/>
+    <col min="13" max="13" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -555,7 +537,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>45443</v>
       </c>
@@ -582,12 +564,8 @@
       <c r="I2" s="5"/>
       <c r="J2" s="2"/>
       <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>45473</v>
       </c>
@@ -615,12 +593,8 @@
       <c r="I3" s="5"/>
       <c r="J3" s="2"/>
       <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>45504</v>
       </c>
@@ -648,12 +622,8 @@
       <c r="I4" s="5"/>
       <c r="J4" s="2"/>
       <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>45535</v>
       </c>
@@ -681,12 +651,8 @@
       <c r="I5" s="5"/>
       <c r="J5" s="2"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>45565</v>
       </c>
@@ -714,12 +680,8 @@
       <c r="I6" s="5"/>
       <c r="J6" s="2"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>45596</v>
       </c>
@@ -747,12 +709,8 @@
       <c r="I7" s="5"/>
       <c r="J7" s="2"/>
       <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>45626</v>
       </c>
@@ -780,12 +738,8 @@
       <c r="I8" s="5"/>
       <c r="J8" s="2"/>
       <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>45657</v>
       </c>
@@ -813,14 +767,8 @@
       <c r="I9" s="5"/>
       <c r="J9" s="2"/>
       <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>45688</v>
       </c>
@@ -848,14 +796,8 @@
       <c r="I10" s="5"/>
       <c r="J10" s="2"/>
       <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>45716</v>
       </c>
@@ -883,14 +825,8 @@
       <c r="I11" s="5"/>
       <c r="J11" s="2"/>
       <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>45747</v>
       </c>
@@ -918,14 +854,8 @@
       <c r="I12" s="5"/>
       <c r="J12" s="2"/>
       <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>45777</v>
       </c>
@@ -953,14 +883,8 @@
       <c r="I13" s="5"/>
       <c r="J13" s="2"/>
       <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>45808</v>
       </c>
@@ -988,14 +912,8 @@
       <c r="I14" s="5"/>
       <c r="J14" s="2"/>
       <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>45838</v>
       </c>
@@ -1023,14 +941,8 @@
       <c r="I15" s="5"/>
       <c r="J15" s="2"/>
       <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>45869</v>
       </c>
@@ -1058,14 +970,8 @@
       <c r="I16" s="5"/>
       <c r="J16" s="2"/>
       <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-    </row>
-    <row r="17" spans="1:46" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>45900</v>
       </c>
@@ -1093,14 +999,8 @@
       <c r="I17" s="5"/>
       <c r="J17" s="2"/>
       <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-    </row>
-    <row r="18" spans="1:46" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>45930</v>
       </c>
@@ -1128,14 +1028,10 @@
       <c r="I18" s="5"/>
       <c r="J18" s="2"/>
       <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="2"/>
+      <c r="M18" s="5"/>
       <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-    </row>
-    <row r="19" spans="1:46" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>45961</v>
       </c>
@@ -1163,43 +1059,10 @@
       <c r="I19" s="5"/>
       <c r="J19" s="2"/>
       <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="2"/>
+      <c r="M19" s="5"/>
       <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
-      <c r="Y19" s="2"/>
-      <c r="Z19" s="2"/>
-      <c r="AA19" s="2"/>
-      <c r="AB19" s="2"/>
-      <c r="AC19" s="2"/>
-      <c r="AD19" s="2"/>
-      <c r="AE19" s="2"/>
-      <c r="AF19" s="2"/>
-      <c r="AG19" s="2"/>
-      <c r="AH19" s="2"/>
-      <c r="AI19" s="2"/>
-      <c r="AJ19" s="2"/>
-      <c r="AK19" s="2"/>
-      <c r="AL19" s="2"/>
-      <c r="AM19" s="2"/>
-      <c r="AN19" s="2"/>
-      <c r="AO19" s="2"/>
-      <c r="AP19" s="2"/>
-      <c r="AQ19" s="2"/>
-      <c r="AR19" s="2"/>
-      <c r="AS19" s="2"/>
-      <c r="AT19" s="2"/>
-    </row>
-    <row r="20" spans="1:46" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>45991</v>
       </c>
@@ -1227,43 +1090,10 @@
       <c r="I20" s="5"/>
       <c r="J20" s="2"/>
       <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="2"/>
+      <c r="M20" s="5"/>
       <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="5"/>
-      <c r="V20" s="5"/>
-      <c r="W20" s="5"/>
-      <c r="X20" s="5"/>
-      <c r="Y20" s="5"/>
-      <c r="Z20" s="5"/>
-      <c r="AA20" s="5"/>
-      <c r="AB20" s="5"/>
-      <c r="AC20" s="5"/>
-      <c r="AD20" s="5"/>
-      <c r="AE20" s="5"/>
-      <c r="AF20" s="5"/>
-      <c r="AG20" s="5"/>
-      <c r="AH20" s="5"/>
-      <c r="AI20" s="5"/>
-      <c r="AJ20" s="5"/>
-      <c r="AK20" s="5"/>
-      <c r="AL20" s="5"/>
-      <c r="AM20" s="5"/>
-      <c r="AN20" s="5"/>
-      <c r="AO20" s="5"/>
-      <c r="AP20" s="5"/>
-      <c r="AQ20" s="5"/>
-      <c r="AR20" s="5"/>
-      <c r="AS20" s="5"/>
-      <c r="AT20" s="5"/>
-    </row>
-    <row r="21" spans="1:46" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>46022</v>
       </c>
@@ -1291,43 +1121,10 @@
       <c r="I21" s="5"/>
       <c r="J21" s="2"/>
       <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="2"/>
+      <c r="M21" s="5"/>
       <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="5"/>
-      <c r="V21" s="5"/>
-      <c r="W21" s="5"/>
-      <c r="X21" s="5"/>
-      <c r="Y21" s="5"/>
-      <c r="Z21" s="5"/>
-      <c r="AA21" s="5"/>
-      <c r="AB21" s="5"/>
-      <c r="AC21" s="5"/>
-      <c r="AD21" s="5"/>
-      <c r="AE21" s="5"/>
-      <c r="AF21" s="5"/>
-      <c r="AG21" s="5"/>
-      <c r="AH21" s="5"/>
-      <c r="AI21" s="5"/>
-      <c r="AJ21" s="5"/>
-      <c r="AK21" s="5"/>
-      <c r="AL21" s="5"/>
-      <c r="AM21" s="5"/>
-      <c r="AN21" s="5"/>
-      <c r="AO21" s="5"/>
-      <c r="AP21" s="5"/>
-      <c r="AQ21" s="5"/>
-      <c r="AR21" s="5"/>
-      <c r="AS21" s="5"/>
-      <c r="AT21" s="5"/>
-    </row>
-    <row r="22" spans="1:46" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>46053</v>
       </c>
@@ -1355,14 +1152,10 @@
       <c r="I22" s="5"/>
       <c r="J22" s="2"/>
       <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="2"/>
+      <c r="M22" s="5"/>
       <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-    </row>
-    <row r="23" spans="1:46" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>46081</v>
       </c>
@@ -1390,14 +1183,10 @@
       <c r="I23" s="5"/>
       <c r="J23" s="2"/>
       <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="2"/>
+      <c r="M23" s="5"/>
       <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-    </row>
-    <row r="24" spans="1:46" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>46112</v>
       </c>
@@ -1405,7 +1194,7 @@
         <v>4.0777428669542379</v>
       </c>
       <c r="C24" s="5">
-        <f t="shared" ref="C24:C35" si="2">B24+C23</f>
+        <f t="shared" ref="C24:C34" si="2">B24+C23</f>
         <v>61.88359721313001</v>
       </c>
       <c r="D24" s="5">
@@ -1425,14 +1214,10 @@
       <c r="I24" s="5"/>
       <c r="J24" s="2"/>
       <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="2"/>
+      <c r="M24" s="5"/>
       <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-    </row>
-    <row r="25" spans="1:46" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>46142</v>
       </c>
@@ -1460,22 +1245,19 @@
       <c r="I25" s="5"/>
       <c r="J25" s="2"/>
       <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
       <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-    </row>
-    <row r="26" spans="1:46" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>46173</v>
       </c>
       <c r="B26" s="5">
-        <v>3.8531711558524697</v>
+        <v>1.9800212112829598</v>
       </c>
       <c r="C26" s="5">
         <f t="shared" si="2"/>
-        <v>69.238260664070708</v>
+        <v>67.365110719501203</v>
       </c>
       <c r="D26" s="5">
         <v>5.609521778535119</v>
@@ -1494,51 +1276,19 @@
       <c r="I26" s="5"/>
       <c r="J26" s="2"/>
       <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
       <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
-      <c r="T26" s="5"/>
-      <c r="U26" s="5"/>
-      <c r="V26" s="5"/>
-      <c r="W26" s="5"/>
-      <c r="X26" s="5"/>
-      <c r="Y26" s="5"/>
-      <c r="Z26" s="5"/>
-      <c r="AA26" s="5"/>
-      <c r="AB26" s="5"/>
-      <c r="AC26" s="5"/>
-      <c r="AD26" s="5"/>
-      <c r="AE26" s="5"/>
-      <c r="AF26" s="5"/>
-      <c r="AG26" s="5"/>
-      <c r="AH26" s="5"/>
-      <c r="AI26" s="5"/>
-      <c r="AJ26" s="5"/>
-      <c r="AK26" s="5"/>
-      <c r="AL26" s="5"/>
-      <c r="AM26" s="5"/>
-      <c r="AN26" s="5"/>
-      <c r="AO26" s="5"/>
-      <c r="AP26" s="5"/>
-      <c r="AQ26" s="5"/>
-      <c r="AR26" s="5"/>
-      <c r="AS26" s="5"/>
-      <c r="AT26" s="5"/>
-    </row>
-    <row r="27" spans="1:46" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>46203</v>
       </c>
       <c r="B27" s="5">
-        <v>4.6786247600919797</v>
+        <v>3.8196937287186921</v>
       </c>
       <c r="C27" s="5">
         <f t="shared" si="2"/>
-        <v>73.916885424162686</v>
+        <v>71.184804448219893</v>
       </c>
       <c r="D27" s="5">
         <v>3.6604000147033013</v>
@@ -1557,51 +1307,19 @@
       <c r="I27" s="5"/>
       <c r="J27" s="2"/>
       <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
       <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-      <c r="S27" s="5"/>
-      <c r="T27" s="5"/>
-      <c r="U27" s="5"/>
-      <c r="V27" s="5"/>
-      <c r="W27" s="5"/>
-      <c r="X27" s="5"/>
-      <c r="Y27" s="5"/>
-      <c r="Z27" s="5"/>
-      <c r="AA27" s="5"/>
-      <c r="AB27" s="5"/>
-      <c r="AC27" s="5"/>
-      <c r="AD27" s="5"/>
-      <c r="AE27" s="5"/>
-      <c r="AF27" s="5"/>
-      <c r="AG27" s="5"/>
-      <c r="AH27" s="5"/>
-      <c r="AI27" s="5"/>
-      <c r="AJ27" s="5"/>
-      <c r="AK27" s="5"/>
-      <c r="AL27" s="5"/>
-      <c r="AM27" s="5"/>
-      <c r="AN27" s="5"/>
-      <c r="AO27" s="5"/>
-      <c r="AP27" s="5"/>
-      <c r="AQ27" s="5"/>
-      <c r="AR27" s="5"/>
-      <c r="AS27" s="5"/>
-      <c r="AT27" s="5"/>
-    </row>
-    <row r="28" spans="1:46" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>46234</v>
       </c>
       <c r="B28" s="5">
-        <v>7.01</v>
+        <v>7.0253553071711403</v>
       </c>
       <c r="C28" s="5">
         <f t="shared" si="2"/>
-        <v>80.926885424162691</v>
+        <v>78.210159755391032</v>
       </c>
       <c r="D28" s="5">
         <v>4.7754104889294844</v>
@@ -1620,22 +1338,19 @@
       <c r="I28" s="5"/>
       <c r="J28" s="2"/>
       <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
       <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-    </row>
-    <row r="29" spans="1:46" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>46265</v>
       </c>
       <c r="B29" s="5">
-        <v>6.0968221609415796</v>
+        <v>6.9159248176517396</v>
       </c>
       <c r="C29" s="5">
         <f t="shared" si="2"/>
-        <v>87.023707585104276</v>
+        <v>85.126084573042775</v>
       </c>
       <c r="D29" s="5">
         <v>4.6533975272671508</v>
@@ -1654,22 +1369,19 @@
       <c r="I29" s="5"/>
       <c r="J29" s="2"/>
       <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
       <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
-    </row>
-    <row r="30" spans="1:46" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>46295</v>
       </c>
       <c r="B30" s="5">
-        <v>3.7564913195156415</v>
+        <v>4.2676820962505104</v>
       </c>
       <c r="C30" s="5">
         <f t="shared" si="2"/>
-        <v>90.780198904619922</v>
+        <v>89.393766669293285</v>
       </c>
       <c r="D30" s="5">
         <v>4.7101274741177823</v>
@@ -1688,22 +1400,19 @@
       <c r="I30" s="5"/>
       <c r="J30" s="2"/>
       <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
       <c r="N30" s="5"/>
-      <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
-      <c r="Q30" s="5"/>
-    </row>
-    <row r="31" spans="1:46" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>46326</v>
       </c>
       <c r="B31" s="5">
-        <v>4.4727637918657246</v>
+        <v>5.075500183191985</v>
       </c>
       <c r="C31" s="5">
         <f t="shared" si="2"/>
-        <v>95.252962696485653</v>
+        <v>94.469266852485276</v>
       </c>
       <c r="D31" s="5">
         <v>3.3851885105485091</v>
@@ -1722,22 +1431,19 @@
       <c r="I31" s="5"/>
       <c r="J31" s="2"/>
       <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
       <c r="N31" s="5"/>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
-    </row>
-    <row r="32" spans="1:46" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>46356</v>
       </c>
       <c r="B32" s="5">
-        <v>1.8648397094426086</v>
+        <v>2.1194876526451707</v>
       </c>
       <c r="C32" s="5">
         <f t="shared" si="2"/>
-        <v>97.117802405928259</v>
+        <v>96.588754505130453</v>
       </c>
       <c r="D32" s="5">
         <v>1.6260930386958057</v>
@@ -1756,22 +1462,19 @@
       <c r="I32" s="5"/>
       <c r="J32" s="2"/>
       <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
       <c r="N32" s="5"/>
-      <c r="O32" s="5"/>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="5"/>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>46387</v>
       </c>
       <c r="B33" s="5">
-        <v>1.3731745642513373</v>
+        <v>1.7573445713320122</v>
       </c>
       <c r="C33" s="5">
         <f t="shared" si="2"/>
-        <v>98.490976970179602</v>
+        <v>98.346099076462465</v>
       </c>
       <c r="D33" s="5">
         <v>1.0526891974688515</v>
@@ -1790,22 +1493,19 @@
       <c r="I33" s="5"/>
       <c r="J33" s="2"/>
       <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
       <c r="N33" s="5"/>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>46418</v>
       </c>
       <c r="B34" s="5">
-        <v>1.1970641274525655</v>
+        <v>1.5999422404766306</v>
       </c>
       <c r="C34" s="5">
         <f t="shared" si="2"/>
-        <v>99.688041097632166</v>
+        <v>99.946041316939102</v>
       </c>
       <c r="D34" s="5">
         <v>1.0108646273378574</v>
@@ -1824,22 +1524,19 @@
       <c r="I34" s="5"/>
       <c r="J34" s="2"/>
       <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
       <c r="N34" s="5"/>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="5"/>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>46446</v>
       </c>
       <c r="B35" s="5">
-        <v>0.31311062960122193</v>
+        <v>5.3958683061537754E-2</v>
       </c>
       <c r="C35" s="5">
-        <f t="shared" si="2"/>
-        <v>100.00115172723339</v>
+        <f>B35+C34</f>
+        <v>100.00000000000064</v>
       </c>
       <c r="D35" s="5">
         <f>100-E34</f>
@@ -1859,13 +1556,10 @@
       <c r="I35" s="5"/>
       <c r="J35" s="2"/>
       <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
       <c r="N35" s="5"/>
-      <c r="O35" s="5"/>
-      <c r="P35" s="5"/>
-      <c r="Q35" s="5"/>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>46477</v>
       </c>
@@ -1874,7 +1568,7 @@
       </c>
       <c r="C36" s="5">
         <f t="shared" si="0"/>
-        <v>100.00115172723339</v>
+        <v>100.00000000000064</v>
       </c>
       <c r="D36" s="5">
         <v>0</v>
@@ -1890,56 +1584,72 @@
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
       <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="5"/>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="5"/>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="P39" s="5"/>
-      <c r="Q39" s="5"/>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="P40" s="5"/>
-      <c r="Q40" s="5"/>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E41" s="6"/>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="P42" s="5"/>
-      <c r="Q42" s="5"/>
-    </row>
-    <row r="55" spans="14:15" x14ac:dyDescent="0.3">
-      <c r="N55" s="5"/>
-      <c r="O55" s="5"/>
-    </row>
-    <row r="56" spans="14:15" x14ac:dyDescent="0.3">
-      <c r="N56" s="5"/>
-      <c r="O56" s="5"/>
-    </row>
-    <row r="57" spans="14:15" x14ac:dyDescent="0.3">
-      <c r="N57" s="5"/>
-      <c r="O57" s="5"/>
-    </row>
-    <row r="58" spans="14:15" x14ac:dyDescent="0.3">
-      <c r="N58" s="5"/>
-      <c r="O58" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+    </row>
+    <row r="49" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+    </row>
+    <row r="50" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+    </row>
+    <row r="51" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1948,9 +1658,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2098,19 +1811,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E7B3CB9-FAE3-4DD3-B62A-E97648FB882B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5587604-DA3E-4313-9FC4-BBB4C884AB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2134,9 +1843,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5587604-DA3E-4313-9FC4-BBB4C884AB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E7B3CB9-FAE3-4DD3-B62A-E97648FB882B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/evolucao.xlsx
+++ b/data/evolucao.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30218"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21AB1958-153C-4430-95A2-F4FA54BA7E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A898D00-72F3-4179-9940-5B2808B3AC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7EB965E4-CD38-43F5-AB1D-C85E27C9787B}"/>
   </bookViews>
@@ -499,7 +499,7 @@
   <sheetPr>
     <outlinePr summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
@@ -511,10 +511,11 @@
     <col min="7" max="7" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="11" width="10.88671875" customWidth="1"/>
     <col min="13" max="13" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -537,7 +538,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>45443</v>
       </c>
@@ -565,7 +566,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="5"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>45473</v>
       </c>
@@ -594,7 +595,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="5"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>45504</v>
       </c>
@@ -623,7 +624,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="5"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>45535</v>
       </c>
@@ -652,7 +653,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>45565</v>
       </c>
@@ -681,7 +682,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="5"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>45596</v>
       </c>
@@ -710,7 +711,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="5"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>45626</v>
       </c>
@@ -739,7 +740,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>45657</v>
       </c>
@@ -768,7 +769,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>45688</v>
       </c>
@@ -797,7 +798,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="5"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>45716</v>
       </c>
@@ -826,7 +827,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>45747</v>
       </c>
@@ -855,7 +856,7 @@
       <c r="J12" s="2"/>
       <c r="K12" s="5"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>45777</v>
       </c>
@@ -883,8 +884,10 @@
       <c r="I13" s="5"/>
       <c r="J13" s="2"/>
       <c r="K13" s="5"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>45808</v>
       </c>
@@ -912,8 +915,10 @@
       <c r="I14" s="5"/>
       <c r="J14" s="2"/>
       <c r="K14" s="5"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>45838</v>
       </c>
@@ -941,8 +946,10 @@
       <c r="I15" s="5"/>
       <c r="J15" s="2"/>
       <c r="K15" s="5"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>45869</v>
       </c>
@@ -970,8 +977,10 @@
       <c r="I16" s="5"/>
       <c r="J16" s="2"/>
       <c r="K16" s="5"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>45900</v>
       </c>
@@ -999,8 +1008,10 @@
       <c r="I17" s="5"/>
       <c r="J17" s="2"/>
       <c r="K17" s="5"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>45930</v>
       </c>
@@ -1030,8 +1041,9 @@
       <c r="K18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O18" s="5"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>45961</v>
       </c>
@@ -1061,8 +1073,9 @@
       <c r="K19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O19" s="5"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>45991</v>
       </c>
@@ -1092,8 +1105,9 @@
       <c r="K20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O20" s="5"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>46022</v>
       </c>
@@ -1123,8 +1137,9 @@
       <c r="K21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O21" s="5"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>46053</v>
       </c>
@@ -1154,8 +1169,9 @@
       <c r="K22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O22" s="5"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>46081</v>
       </c>
@@ -1185,8 +1201,9 @@
       <c r="K23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O23" s="5"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>46112</v>
       </c>
@@ -1216,8 +1233,9 @@
       <c r="K24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O24" s="5"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>46142</v>
       </c>
@@ -1247,8 +1265,9 @@
       <c r="K25" s="5"/>
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O25" s="5"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>46173</v>
       </c>
@@ -1278,17 +1297,18 @@
       <c r="K26" s="5"/>
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O26" s="5"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>46203</v>
       </c>
       <c r="B27" s="5">
-        <v>3.8196937287186921</v>
+        <v>3.0593938532748828</v>
       </c>
       <c r="C27" s="5">
         <f t="shared" si="2"/>
-        <v>71.184804448219893</v>
+        <v>70.424504572776087</v>
       </c>
       <c r="D27" s="5">
         <v>3.6604000147033013</v>
@@ -1309,17 +1329,18 @@
       <c r="K27" s="5"/>
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O27" s="5"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>46234</v>
       </c>
       <c r="B28" s="5">
-        <v>7.0253553071711403</v>
+        <v>4.813671510339069</v>
       </c>
       <c r="C28" s="5">
         <f t="shared" si="2"/>
-        <v>78.210159755391032</v>
+        <v>75.23817608311515</v>
       </c>
       <c r="D28" s="5">
         <v>4.7754104889294844</v>
@@ -1340,17 +1361,18 @@
       <c r="K28" s="5"/>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O28" s="5"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>46265</v>
       </c>
       <c r="B29" s="5">
-        <v>6.9159248176517396</v>
+        <v>4.4729125462378745</v>
       </c>
       <c r="C29" s="5">
         <f t="shared" si="2"/>
-        <v>85.126084573042775</v>
+        <v>79.711088629353029</v>
       </c>
       <c r="D29" s="5">
         <v>4.6533975272671508</v>
@@ -1371,17 +1393,18 @@
       <c r="K29" s="5"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O29" s="5"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>46295</v>
       </c>
       <c r="B30" s="5">
-        <v>4.2676820962505104</v>
+        <v>5.3026378252240711</v>
       </c>
       <c r="C30" s="5">
         <f t="shared" si="2"/>
-        <v>89.393766669293285</v>
+        <v>85.013726454577096</v>
       </c>
       <c r="D30" s="5">
         <v>4.7101274741177823</v>
@@ -1402,17 +1425,18 @@
       <c r="K30" s="5"/>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O30" s="5"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>46326</v>
       </c>
       <c r="B31" s="5">
-        <v>5.075500183191985</v>
+        <v>5.1278325364587891</v>
       </c>
       <c r="C31" s="5">
         <f t="shared" si="2"/>
-        <v>94.469266852485276</v>
+        <v>90.141558991035879</v>
       </c>
       <c r="D31" s="5">
         <v>3.3851885105485091</v>
@@ -1433,17 +1457,18 @@
       <c r="K31" s="5"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O31" s="5"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>46356</v>
       </c>
       <c r="B32" s="5">
-        <v>2.1194876526451707</v>
+        <v>3.508283821803476</v>
       </c>
       <c r="C32" s="5">
         <f t="shared" si="2"/>
-        <v>96.588754505130453</v>
+        <v>93.649842812839353</v>
       </c>
       <c r="D32" s="5">
         <v>1.6260930386958057</v>
@@ -1464,17 +1489,18 @@
       <c r="K32" s="5"/>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O32" s="5"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>46387</v>
       </c>
       <c r="B33" s="5">
-        <v>1.7573445713320122</v>
+        <v>2.6748352922757355</v>
       </c>
       <c r="C33" s="5">
         <f t="shared" si="2"/>
-        <v>98.346099076462465</v>
+        <v>96.324678105115083</v>
       </c>
       <c r="D33" s="5">
         <v>1.0526891974688515</v>
@@ -1495,17 +1521,18 @@
       <c r="K33" s="5"/>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O33" s="5"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>46418</v>
       </c>
       <c r="B34" s="5">
-        <v>1.5999422404766306</v>
+        <v>3.0534141028217081</v>
       </c>
       <c r="C34" s="5">
         <f t="shared" si="2"/>
-        <v>99.946041316939102</v>
+        <v>99.378092207936788</v>
       </c>
       <c r="D34" s="5">
         <v>1.0108646273378574</v>
@@ -1526,17 +1553,18 @@
       <c r="K34" s="5"/>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O34" s="5"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>46446</v>
       </c>
       <c r="B35" s="5">
-        <v>5.3958683061537754E-2</v>
+        <v>0.48319525346671605</v>
       </c>
       <c r="C35" s="5">
         <f>B35+C34</f>
-        <v>100.00000000000064</v>
+        <v>99.861287461403506</v>
       </c>
       <c r="D35" s="5">
         <f>100-E34</f>
@@ -1558,17 +1586,19 @@
       <c r="K35" s="5"/>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O35" s="5"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>46477</v>
       </c>
       <c r="B36" s="5">
-        <v>0</v>
+        <f>100-C35</f>
+        <v>0.13871253859649357</v>
       </c>
       <c r="C36" s="5">
         <f t="shared" si="0"/>
-        <v>100.00000000000064</v>
+        <v>100</v>
       </c>
       <c r="D36" s="5">
         <v>0</v>
@@ -1586,56 +1616,68 @@
       <c r="K36" s="5"/>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O36" s="5"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K37" s="5"/>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O37" s="5"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K38" s="5"/>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O38" s="5"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O39" s="5"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O40" s="5"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E41" s="6"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O41" s="5"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O42" s="5"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O43" s="5"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O44" s="5"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O45" s="5"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O46" s="5"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O47" s="5"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
     </row>

--- a/data/evolucao.xlsx
+++ b/data/evolucao.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30218"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A898D00-72F3-4179-9940-5B2808B3AC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93C7A9A-85A1-4833-B842-08359ED3AEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7EB965E4-CD38-43F5-AB1D-C85E27C9787B}"/>
   </bookViews>
@@ -1336,11 +1336,11 @@
         <v>46234</v>
       </c>
       <c r="B28" s="5">
-        <v>4.813671510339069</v>
+        <v>3.6143944093964695</v>
       </c>
       <c r="C28" s="5">
         <f t="shared" si="2"/>
-        <v>75.23817608311515</v>
+        <v>74.038898982172554</v>
       </c>
       <c r="D28" s="5">
         <v>4.7754104889294844</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="C29" s="5">
         <f t="shared" si="2"/>
-        <v>79.711088629353029</v>
+        <v>78.511811528410433</v>
       </c>
       <c r="D29" s="5">
         <v>4.6533975272671508</v>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="C30" s="5">
         <f t="shared" si="2"/>
-        <v>85.013726454577096</v>
+        <v>83.814449353634501</v>
       </c>
       <c r="D30" s="5">
         <v>4.7101274741177823</v>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C31" s="5">
         <f t="shared" si="2"/>
-        <v>90.141558991035879</v>
+        <v>88.942281890093284</v>
       </c>
       <c r="D31" s="5">
         <v>3.3851885105485091</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="C32" s="5">
         <f t="shared" si="2"/>
-        <v>93.649842812839353</v>
+        <v>92.450565711896758</v>
       </c>
       <c r="D32" s="5">
         <v>1.6260930386958057</v>
@@ -1487,8 +1487,6 @@
       <c r="I32" s="5"/>
       <c r="J32" s="2"/>
       <c r="K32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
       <c r="O32" s="5"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
@@ -1500,7 +1498,7 @@
       </c>
       <c r="C33" s="5">
         <f t="shared" si="2"/>
-        <v>96.324678105115083</v>
+        <v>95.125401004172488</v>
       </c>
       <c r="D33" s="5">
         <v>1.0526891974688515</v>
@@ -1519,8 +1517,6 @@
       <c r="I33" s="5"/>
       <c r="J33" s="2"/>
       <c r="K33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
       <c r="O33" s="5"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
@@ -1532,7 +1528,7 @@
       </c>
       <c r="C34" s="5">
         <f t="shared" si="2"/>
-        <v>99.378092207936788</v>
+        <v>98.178815106994193</v>
       </c>
       <c r="D34" s="5">
         <v>1.0108646273378574</v>
@@ -1551,8 +1547,6 @@
       <c r="I34" s="5"/>
       <c r="J34" s="2"/>
       <c r="K34" s="5"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
       <c r="O34" s="5"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
@@ -1564,7 +1558,7 @@
       </c>
       <c r="C35" s="5">
         <f>B35+C34</f>
-        <v>99.861287461403506</v>
+        <v>98.662010360460911</v>
       </c>
       <c r="D35" s="5">
         <f>100-E34</f>
@@ -1584,8 +1578,6 @@
       <c r="I35" s="5"/>
       <c r="J35" s="2"/>
       <c r="K35" s="5"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
       <c r="O35" s="5"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
@@ -1594,7 +1586,7 @@
       </c>
       <c r="B36" s="5">
         <f>100-C35</f>
-        <v>0.13871253859649357</v>
+        <v>1.3379896395390887</v>
       </c>
       <c r="C36" s="5">
         <f t="shared" si="0"/>
@@ -1614,14 +1606,10 @@
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
       <c r="O36" s="5"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K37" s="5"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
       <c r="O37" s="5"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
@@ -1700,15 +1688,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101000D4A9A36208A5B4AA3E00F236CB017CA" ma:contentTypeVersion="4" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="82545827fb752ba7757bc26eede0d32f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d0424105-a063-48c1-bff7-c278edf1bbf4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="300b5507c0a1c8faa7ef79fe86b62e4a" ns2:_="">
     <xsd:import namespace="d0424105-a063-48c1-bff7-c278edf1bbf4"/>
@@ -1852,6 +1831,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -1859,14 +1847,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5587604-DA3E-4313-9FC4-BBB4C884AB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2713E33-8478-4908-9D78-1EC1E27B51EA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1884,6 +1864,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5587604-DA3E-4313-9FC4-BBB4C884AB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E7B3CB9-FAE3-4DD3-B62A-E97648FB882B}">
   <ds:schemaRefs>

--- a/data/evolucao.xlsx
+++ b/data/evolucao.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93C7A9A-85A1-4833-B842-08359ED3AEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{F93C7A9A-85A1-4833-B842-08359ED3AEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8FB8DFA-72CC-44FD-A2C8-737BDEEEF993}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7EB965E4-CD38-43F5-AB1D-C85E27C9787B}"/>
   </bookViews>
@@ -499,7 +499,7 @@
   <sheetPr>
     <outlinePr summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:Q54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
@@ -1070,7 +1070,8 @@
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="2"/>
-      <c r="K19" s="5"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
@@ -1102,7 +1103,8 @@
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="2"/>
-      <c r="K20" s="5"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
@@ -1134,7 +1136,8 @@
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
       <c r="J21" s="2"/>
-      <c r="K21" s="5"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
@@ -1166,7 +1169,8 @@
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="2"/>
-      <c r="K22" s="5"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
@@ -1198,7 +1202,8 @@
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="2"/>
-      <c r="K23" s="5"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
@@ -1230,7 +1235,8 @@
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="2"/>
-      <c r="K24" s="5"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
@@ -1262,7 +1268,8 @@
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="2"/>
-      <c r="K25" s="5"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="5"/>
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
@@ -1294,7 +1301,8 @@
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
       <c r="J26" s="2"/>
-      <c r="K26" s="5"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="5"/>
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
@@ -1326,7 +1334,8 @@
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
       <c r="J27" s="2"/>
-      <c r="K27" s="5"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="5"/>
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
@@ -1358,7 +1367,8 @@
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="2"/>
-      <c r="K28" s="5"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="5"/>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
@@ -1368,11 +1378,11 @@
         <v>46265</v>
       </c>
       <c r="B29" s="5">
-        <v>4.4729125462378745</v>
+        <v>3.5290684827717387</v>
       </c>
       <c r="C29" s="5">
         <f t="shared" si="2"/>
-        <v>78.511811528410433</v>
+        <v>77.567967464944289</v>
       </c>
       <c r="D29" s="5">
         <v>4.6533975272671508</v>
@@ -1390,7 +1400,8 @@
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
       <c r="J29" s="2"/>
-      <c r="K29" s="5"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="5"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
@@ -1400,11 +1411,11 @@
         <v>46295</v>
       </c>
       <c r="B30" s="5">
-        <v>5.3026378252240711</v>
+        <v>5.6845255987694063</v>
       </c>
       <c r="C30" s="5">
         <f t="shared" si="2"/>
-        <v>83.814449353634501</v>
+        <v>83.2524930637137</v>
       </c>
       <c r="D30" s="5">
         <v>4.7101274741177823</v>
@@ -1422,7 +1433,8 @@
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="2"/>
-      <c r="K30" s="5"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="5"/>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
@@ -1432,11 +1444,11 @@
         <v>46326</v>
       </c>
       <c r="B31" s="5">
-        <v>5.1278325364587891</v>
+        <v>5.9822389525994231</v>
       </c>
       <c r="C31" s="5">
         <f t="shared" si="2"/>
-        <v>88.942281890093284</v>
+        <v>89.234732016313117</v>
       </c>
       <c r="D31" s="5">
         <v>3.3851885105485091</v>
@@ -1454,7 +1466,8 @@
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="2"/>
-      <c r="K31" s="5"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="5"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
@@ -1464,11 +1477,11 @@
         <v>46356</v>
       </c>
       <c r="B32" s="5">
-        <v>3.508283821803476</v>
+        <v>3.1334905668686135</v>
       </c>
       <c r="C32" s="5">
         <f t="shared" si="2"/>
-        <v>92.450565711896758</v>
+        <v>92.368222583181733</v>
       </c>
       <c r="D32" s="5">
         <v>1.6260930386958057</v>
@@ -1486,7 +1499,10 @@
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="5"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
       <c r="O32" s="5"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
@@ -1494,11 +1510,11 @@
         <v>46387</v>
       </c>
       <c r="B33" s="5">
-        <v>2.6748352922757355</v>
+        <v>3.4391851167996186</v>
       </c>
       <c r="C33" s="5">
         <f t="shared" si="2"/>
-        <v>95.125401004172488</v>
+        <v>95.807407699981354</v>
       </c>
       <c r="D33" s="5">
         <v>1.0526891974688515</v>
@@ -1516,7 +1532,10 @@
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="2"/>
-      <c r="K33" s="5"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
       <c r="O33" s="5"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
@@ -1524,11 +1543,11 @@
         <v>46418</v>
       </c>
       <c r="B34" s="5">
-        <v>3.0534141028217081</v>
+        <v>2.20563903450598</v>
       </c>
       <c r="C34" s="5">
         <f t="shared" si="2"/>
-        <v>98.178815106994193</v>
+        <v>98.013046734487332</v>
       </c>
       <c r="D34" s="5">
         <v>1.0108646273378574</v>
@@ -1546,7 +1565,10 @@
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
       <c r="J34" s="2"/>
-      <c r="K34" s="5"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
       <c r="O34" s="5"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
@@ -1554,11 +1576,11 @@
         <v>46446</v>
       </c>
       <c r="B35" s="5">
-        <v>0.48319525346671605</v>
+        <v>1.7271093044575019</v>
       </c>
       <c r="C35" s="5">
         <f>B35+C34</f>
-        <v>98.662010360460911</v>
+        <v>99.740156038944832</v>
       </c>
       <c r="D35" s="5">
         <f>100-E34</f>
@@ -1577,7 +1599,10 @@
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="2"/>
-      <c r="K35" s="5"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
       <c r="O35" s="5"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
@@ -1585,8 +1610,7 @@
         <v>46477</v>
       </c>
       <c r="B36" s="5">
-        <f>100-C35</f>
-        <v>1.3379896395390887</v>
+        <v>0.25984396105516283</v>
       </c>
       <c r="C36" s="5">
         <f t="shared" si="0"/>
@@ -1605,81 +1629,123 @@
         <v>100.00000000000061</v>
       </c>
       <c r="J36" s="2"/>
-      <c r="K36" s="5"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
       <c r="O36" s="5"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="K37" s="5"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
       <c r="O37" s="5"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="K38" s="5"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="5"/>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
       <c r="O38" s="5"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="K39" s="2"/>
+      <c r="L39" s="5"/>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
       <c r="O39" s="5"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="K40" s="2"/>
+      <c r="L40" s="5"/>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E41" s="6"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="5"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
       <c r="O41" s="5"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="K42" s="2"/>
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
       <c r="O42" s="5"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="K43" s="2"/>
+      <c r="L43" s="5"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
       <c r="O43" s="5"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="K44" s="2"/>
+      <c r="L44" s="5"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
       <c r="O44" s="5"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="K45" s="2"/>
+      <c r="L45" s="5"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
       <c r="O45" s="5"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
       <c r="O46" s="5"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
       <c r="O47" s="5"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
-    </row>
-    <row r="49" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="O48" s="5"/>
+    </row>
+    <row r="49" spans="12:17" x14ac:dyDescent="0.3">
+      <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
-    </row>
-    <row r="50" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="O49" s="5"/>
+    </row>
+    <row r="50" spans="12:17" x14ac:dyDescent="0.3">
+      <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
-    </row>
-    <row r="51" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="O50" s="5"/>
+    </row>
+    <row r="51" spans="12:17" x14ac:dyDescent="0.3">
+      <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+    </row>
+    <row r="52" spans="12:17" x14ac:dyDescent="0.3">
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+    </row>
+    <row r="53" spans="12:17" x14ac:dyDescent="0.3">
+      <c r="M53" s="5"/>
+    </row>
+    <row r="54" spans="12:17" x14ac:dyDescent="0.3">
+      <c r="Q54" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1688,6 +1754,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101000D4A9A36208A5B4AA3E00F236CB017CA" ma:contentTypeVersion="4" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="82545827fb752ba7757bc26eede0d32f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d0424105-a063-48c1-bff7-c278edf1bbf4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="300b5507c0a1c8faa7ef79fe86b62e4a" ns2:_="">
     <xsd:import namespace="d0424105-a063-48c1-bff7-c278edf1bbf4"/>
@@ -1831,22 +1912,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E7B3CB9-FAE3-4DD3-B62A-E97648FB882B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5587604-DA3E-4313-9FC4-BBB4C884AB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2713E33-8478-4908-9D78-1EC1E27B51EA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1862,21 +1945,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5587604-DA3E-4313-9FC4-BBB4C884AB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E7B3CB9-FAE3-4DD3-B62A-E97648FB882B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>